--- a/extra/report/No5_バッチ処理テスト結果.xlsx
+++ b/extra/report/No5_バッチ処理テスト結果.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C74918A-A97B-4814-BA08-FEFAC83A19B0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB431376-F030-401B-A0C1-EFFD2F5AF21A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="前提条件" sheetId="1" r:id="rId1"/>
@@ -491,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -516,6 +516,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="55" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="55" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -537,23 +543,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>47</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>56030</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>51469</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>67</xdr:col>
-      <xdr:colOff>673006</xdr:colOff>
-      <xdr:row>176</xdr:row>
-      <xdr:rowOff>48563</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>96859</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>101666</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="図 54">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B5F9694-FA80-4EBC-B5A5-280BDB3FF794}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1DA4A2B-1FBC-4597-8F34-CD82DBA83765}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -569,8 +575,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13659971" y="22747942"/>
-          <a:ext cx="12708123" cy="6716062"/>
+          <a:off x="0" y="1289719"/>
+          <a:ext cx="11486038" cy="6241447"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -581,23 +587,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>44824</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>51469</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>168741</xdr:colOff>
-      <xdr:row>176</xdr:row>
-      <xdr:rowOff>37357</xdr:rowOff>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>650138</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>101666</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="図 53">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE1BEBD2-78C3-4DE7-BF7E-FBC1EAD82CA8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0625B83-40B3-488B-A3F5-F8AD012BC97F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -613,272 +619,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="22736736"/>
-          <a:ext cx="12708123" cy="6716062"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>33617</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>67</xdr:col>
-      <xdr:colOff>673006</xdr:colOff>
-      <xdr:row>133</xdr:row>
-      <xdr:rowOff>26150</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="図 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F53F5F24-BF41-4583-89C3-E823448B19D7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13166912" y="15497735"/>
-          <a:ext cx="12708123" cy="6716062"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>168741</xdr:colOff>
-      <xdr:row>132</xdr:row>
-      <xdr:rowOff>160621</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="図 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C96D51C-EBE3-4F17-B6AA-F7678F4998AB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="15464118"/>
-          <a:ext cx="12708123" cy="6716062"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>67</xdr:col>
-      <xdr:colOff>673006</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>160621</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="図 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7599281C-9903-40AF-95D3-E839D904A8B5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13166912" y="8236324"/>
-          <a:ext cx="12708123" cy="6716062"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>168741</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>160621</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="図 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17598B59-EB5C-4E03-8959-A18258A7181A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="8236324"/>
-          <a:ext cx="12708123" cy="6716062"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>67</xdr:col>
-      <xdr:colOff>673006</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>160621</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="図 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{497F44FB-A54C-46A6-BB89-04315AB7F012}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13166912" y="1008529"/>
-          <a:ext cx="12708123" cy="6716062"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>168741</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>160621</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="図 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4A19B8F-D877-4DFE-930F-69F89F177A3D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="1008529"/>
-          <a:ext cx="12708123" cy="6716062"/>
+          <a:off x="13294179" y="1289719"/>
+          <a:ext cx="11421552" cy="6241447"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -889,946 +631,1154 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>134471</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>33620</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>145677</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>156883</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>96859</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>101666</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="正方形/長方形 9">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="37" name="グループ化 36">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A292636-390A-4A65-A094-17DE3446A6D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB428BCF-3303-447A-A75B-DF3390ED2530}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2095500" y="11799796"/>
-          <a:ext cx="8695765" cy="627528"/>
+          <a:off x="0" y="8626928"/>
+          <a:ext cx="11641159" cy="6047988"/>
+          <a:chOff x="0" y="8626928"/>
+          <a:chExt cx="11641159" cy="6047988"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="4" name="図 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D3B3473-6321-41B3-996D-0F9944FB6F3D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="0" y="8626928"/>
+            <a:ext cx="11641159" cy="6047988"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="36" name="グループ化 35">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EC38503-2293-4E32-BBDA-90AD5F9C4140}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="2095500" y="12158945"/>
+            <a:ext cx="9141277" cy="1611483"/>
+            <a:chOff x="2095500" y="12158945"/>
+            <a:chExt cx="9141277" cy="1611483"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10" name="正方形/長方形 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A292636-390A-4A65-A094-17DE3446A6D7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2095501" y="12158945"/>
+              <a:ext cx="8822952" cy="637613"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="正方形/長方形 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08E5756A-B59C-4FC1-A4FB-F1B16CE9F40A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2095500" y="12982575"/>
+              <a:ext cx="8813427" cy="203953"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="テキスト ボックス 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F2D1CAA-FC64-4756-8FC0-DD2ABB064BA5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10585076" y="13395513"/>
+              <a:ext cx="651701" cy="374915"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>4</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>件</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>107575</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>22410</xdr:rowOff>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>145677</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>51553</xdr:rowOff>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>650138</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>101666</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="正方形/長方形 10">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="35" name="グループ化 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08E5756A-B59C-4FC1-A4FB-F1B16CE9F40A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E349B19-4C6D-4C1B-842A-70A708EBCC6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2068604" y="12629028"/>
-          <a:ext cx="8722661" cy="197231"/>
+          <a:off x="13477875" y="8626928"/>
+          <a:ext cx="11518163" cy="6047988"/>
+          <a:chOff x="13477875" y="8626928"/>
+          <a:chExt cx="11518163" cy="6047988"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="26" name="グループ化 25">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{416AA810-71F9-4A44-A531-09D9D7CB56D1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="13477875" y="8626928"/>
+            <a:ext cx="11518163" cy="6047988"/>
+            <a:chOff x="13477875" y="8626928"/>
+            <a:chExt cx="11518163" cy="6047988"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="図 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8740DE7-99FF-4164-AC29-0E8A71FFB4A0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13477875" y="8626928"/>
+              <a:ext cx="11518163" cy="6047988"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="38" name="正方形/長方形 37">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F445715-21B4-4ADE-AE62-A8D64BAD5514}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15582901" y="12163425"/>
+              <a:ext cx="6896099" cy="637613"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="39" name="正方形/長方形 38">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91BC3977-72E5-4C3A-B90D-CE463ACC07A9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15582901" y="12987055"/>
+              <a:ext cx="6888654" cy="203953"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="21" name="テキスト ボックス 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BAFD70D-8466-46A7-9844-519BAC0544E7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="22451548" y="13365257"/>
+            <a:ext cx="537882" cy="391085"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>4</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>件</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>679094</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>17935</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>63</xdr:col>
-      <xdr:colOff>67234</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>2</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>96859</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>101667</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="正方形/長方形 12">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="40" name="グループ化 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21495C8E-2C26-432F-A487-7920C31A78D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53C8012D-C50A-4AAB-B79D-77059651E00A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15246741" y="11784111"/>
-          <a:ext cx="6907287" cy="654420"/>
+          <a:off x="0" y="15999278"/>
+          <a:ext cx="11641159" cy="6047989"/>
+          <a:chOff x="0" y="15999278"/>
+          <a:chExt cx="11641159" cy="6047989"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="18" name="グループ化 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EE9D3B7-DCD9-497A-A6B3-319F8E275538}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="0" y="15999278"/>
+            <a:ext cx="11641159" cy="6047989"/>
+            <a:chOff x="0" y="15999278"/>
+            <a:chExt cx="11641159" cy="6047989"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="図 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAC05305-2838-4E2D-B1A7-54D7FC021436}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="15999278"/>
+              <a:ext cx="11641159" cy="6047989"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="正方形/長方形 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC903896-1946-485A-A7ED-C143BBD4000D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2119588" y="19946470"/>
+              <a:ext cx="8796061" cy="618564"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="23" name="テキスト ボックス 22">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B49C6782-FB9F-42D1-A16F-784ABA3F83CB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10587317" y="20733126"/>
+            <a:ext cx="608640" cy="347060"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>3</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>件</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>53</xdr:col>
-      <xdr:colOff>2257</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>44823</xdr:rowOff>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>63</xdr:col>
-      <xdr:colOff>67234</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>62757</xdr:rowOff>
+      <xdr:colOff>650138</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>101667</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="正方形/長方形 13">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="41" name="グループ化 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{841B94FC-7634-4E40-B1A7-C86F538A5F97}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B44EA39E-4A6F-4178-854B-8F5B1FFD78A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15253463" y="12651441"/>
-          <a:ext cx="6900565" cy="186022"/>
+          <a:off x="13477875" y="15999278"/>
+          <a:ext cx="11518163" cy="6047989"/>
+          <a:chOff x="13477875" y="15999278"/>
+          <a:chExt cx="11518163" cy="6047989"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="24" name="グループ化 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEA4AC61-61CC-47B7-95F1-D17A5D932428}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="13477875" y="15999278"/>
+            <a:ext cx="11518163" cy="6047989"/>
+            <a:chOff x="13477875" y="15999278"/>
+            <a:chExt cx="11518163" cy="6047989"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="9" name="図 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22FD0747-659B-40C1-BBE0-F0A19AEB492B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13477875" y="15999278"/>
+              <a:ext cx="11518163" cy="6047989"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="正方形/長方形 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19AB3B5F-2D06-4C92-A4BC-E5A2F4424660}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15569467" y="19929126"/>
+              <a:ext cx="6871433" cy="616299"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="25" name="テキスト ボックス 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{821A47CC-F0E2-44A1-8B9A-F14079FE6BD2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="22140583" y="20728642"/>
+            <a:ext cx="537882" cy="388843"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>3</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>件</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>109814</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>134470</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>168089</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>67234</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>96859</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>101666</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="正方形/長方形 16">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="15" name="グループ化 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC903896-1946-485A-A7ED-C143BBD4000D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D635FC7-27E9-4AEA-A91E-4E946C3E556A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2070843" y="19464617"/>
-          <a:ext cx="8742834" cy="605117"/>
+          <a:off x="0" y="23371628"/>
+          <a:ext cx="11641159" cy="6047988"/>
+          <a:chOff x="0" y="23371628"/>
+          <a:chExt cx="11641159" cy="6047988"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="6" name="図 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6D7DEFB-6B6C-4681-8410-83AA8E6A2103}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="0" y="23371628"/>
+            <a:ext cx="11641159" cy="6047988"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="57" name="テキスト ボックス 56">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7987D403-DC18-4ED7-8B27-39885D361B9F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="9334500" y="28494318"/>
+            <a:ext cx="1978399" cy="365312"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>該当なし（</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>0</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>件）</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>672367</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>145701</xdr:rowOff>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>63</xdr:col>
-      <xdr:colOff>44823</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
+      <xdr:colOff>650138</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>101666</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="正方形/長方形 18">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="16" name="グループ化 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19AB3B5F-2D06-4C92-A4BC-E5A2F4424660}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20A31FDF-5391-42B4-95A2-535C4C38061D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15240014" y="19475848"/>
-          <a:ext cx="6891603" cy="627505"/>
+          <a:off x="13477875" y="23371628"/>
+          <a:ext cx="11518163" cy="6047988"/>
+          <a:chOff x="13477875" y="23371628"/>
+          <a:chExt cx="11518163" cy="6047988"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>145677</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>22413</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>123265</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>67236</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="テキスト ボックス 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F2D1CAA-FC64-4756-8FC0-DD2ABB064BA5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10230971" y="12965207"/>
-          <a:ext cx="537882" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="12" name="図 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23A4113C-A690-4FCA-85ED-C9741CD1ACA1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13477875" y="23371628"/>
+            <a:ext cx="11518163" cy="6047988"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="59" name="テキスト ボックス 58">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0880A1D9-8120-4A75-AB92-6F011704F350}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="21561799" y="28423720"/>
+            <a:ext cx="2012576" cy="365312"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
           <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>4</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>件</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>62</xdr:col>
-      <xdr:colOff>96373</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>163607</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>62</xdr:col>
-      <xdr:colOff>634255</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>40342</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="テキスト ボックス 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BAFD70D-8466-46A7-9844-519BAC0544E7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21499608" y="12938313"/>
-          <a:ext cx="537882" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>4</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>件</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>76</xdr:col>
-      <xdr:colOff>271183</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>136713</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>77</xdr:col>
-      <xdr:colOff>125506</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>13448</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="テキスト ボックス 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB42F609-5A5A-4AAA-AA0B-258D49E0A2D6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="31244242" y="12911419"/>
-          <a:ext cx="537882" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>4</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>件</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>147917</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>159125</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>125505</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>33618</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="テキスト ボックス 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B49C6782-FB9F-42D1-A16F-784ABA3F83CB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10233211" y="20161625"/>
-          <a:ext cx="537882" cy="378758"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>3</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>件</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>62</xdr:col>
-      <xdr:colOff>42583</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>154642</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>62</xdr:col>
-      <xdr:colOff>580465</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>29135</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="テキスト ボックス 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{821A47CC-F0E2-44A1-8B9A-F14079FE6BD2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21445818" y="20157142"/>
-          <a:ext cx="537882" cy="378758"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>3</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>件</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>166</xdr:row>
-      <xdr:rowOff>33618</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>44824</xdr:colOff>
-      <xdr:row>168</xdr:row>
-      <xdr:rowOff>56030</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="テキスト ボックス 56">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7987D403-DC18-4ED7-8B27-39885D361B9F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9457765" y="27768177"/>
-          <a:ext cx="2005853" cy="358588"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>該当なし（</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>0</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>件）</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>61</xdr:col>
-      <xdr:colOff>44824</xdr:colOff>
-      <xdr:row>165</xdr:row>
-      <xdr:rowOff>134470</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>64</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>167</xdr:row>
-      <xdr:rowOff>156882</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="59" name="テキスト ボックス 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0880A1D9-8120-4A75-AB92-6F011704F350}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21638559" y="27700941"/>
-          <a:ext cx="2005853" cy="358588"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>該当なし（</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>0</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>件）</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>該当なし（</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>0</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>件）</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -1857,8 +1807,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1035325" y="31647848"/>
-          <a:ext cx="16134522" cy="4108174"/>
+          <a:off x="1036567" y="31198102"/>
+          <a:ext cx="17839497" cy="4048540"/>
           <a:chOff x="1855304" y="35938239"/>
           <a:chExt cx="16134522" cy="4108174"/>
         </a:xfrm>
@@ -2102,16 +2052,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>211435</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>1292</xdr:rowOff>
+      <xdr:colOff>278119</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>163216</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83E4D34D-9CF9-4C99-A403-FCFA19BD303C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3DDED88-A92F-4867-A855-2AEEC1CD8AE5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2128,7 +2078,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="1885950"/>
-          <a:ext cx="13508335" cy="9259592"/>
+          <a:ext cx="13575019" cy="9250066"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2140,13 +2090,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2076449</xdr:colOff>
+      <xdr:colOff>2057399</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>28574</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>28574</xdr:colOff>
+      <xdr:colOff>9524</xdr:colOff>
       <xdr:row>53</xdr:row>
       <xdr:rowOff>152399</xdr:rowOff>
     </xdr:to>
@@ -2163,7 +2113,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2076449" y="8601074"/>
+          <a:off x="2057399" y="8601074"/>
           <a:ext cx="8505825" cy="1838325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2941,16 +2891,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>478135</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>1292</xdr:rowOff>
+      <xdr:colOff>544819</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>163216</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BA854AC-9BC8-4B80-9D7E-0F4FDC6EAF1D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4A3A30A-EFB9-47EB-A9E1-5016370426A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2967,7 +2917,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="685800"/>
-          <a:ext cx="13508335" cy="9259592"/>
+          <a:ext cx="13575019" cy="9250066"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2990,16 +2940,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>478135</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>1292</xdr:rowOff>
+      <xdr:colOff>544819</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>163216</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5D9541C-90B6-4FE3-8FEE-97E03C99314E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D195813-D409-469F-AAA7-8DC942824ACA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3016,7 +2966,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="685800"/>
-          <a:ext cx="13508335" cy="9259592"/>
+          <a:ext cx="13575019" cy="9250066"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3372,23 +3322,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>478135</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>1292</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>544819</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>163216</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{006E2B88-FD16-418F-B6B1-7E92DEA6523D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11B56C6A-C3A4-462E-9D13-2E7245F05922}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3404,8 +3354,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="13508335" cy="9259592"/>
+          <a:off x="685800" y="685800"/>
+          <a:ext cx="13575019" cy="9250066"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3543,16 +3493,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>478135</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>1292</xdr:rowOff>
+      <xdr:colOff>544819</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>163216</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8267656A-8540-4164-8F69-61D4596ACF1C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBFF3572-DF07-465A-B3DF-9DD8426A60F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3569,7 +3519,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="685800"/>
-          <a:ext cx="13508335" cy="9259592"/>
+          <a:ext cx="13575019" cy="9250066"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3822,16 +3772,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>20935</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>29512</xdr:rowOff>
+      <xdr:colOff>87619</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>10555</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DB599EF-C8D5-48A1-B819-014F0118B00B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{031E9837-1B97-4F3D-95EE-3ACDE314A001}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3848,7 +3798,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="2571750"/>
-          <a:ext cx="13508335" cy="6716062"/>
+          <a:ext cx="13575019" cy="7382905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3937,16 +3887,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>497185</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>143900</xdr:rowOff>
+      <xdr:colOff>563869</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>10555</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCB0D0AB-9749-40E9-8D31-42B3EE5592DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5C5501A-6A3C-40DC-A017-464EE2B8A6D9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3963,7 +3913,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="1714500"/>
-          <a:ext cx="13508335" cy="7344800"/>
+          <a:ext cx="13575019" cy="7382905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3975,13 +3925,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2085974</xdr:colOff>
+      <xdr:colOff>2047874</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>85724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>304799</xdr:colOff>
+      <xdr:colOff>266699</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
@@ -3998,7 +3948,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2085974" y="4886324"/>
+          <a:off x="2047874" y="4886324"/>
           <a:ext cx="8486775" cy="3533775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4041,13 +3991,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2057400</xdr:colOff>
+      <xdr:colOff>2019300</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2609850</xdr:colOff>
+      <xdr:colOff>2571750</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
@@ -4064,7 +4014,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2057400" y="8391525"/>
+          <a:off x="2019300" y="8391525"/>
           <a:ext cx="552450" cy="200025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4348,16 +4298,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>573385</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>143900</xdr:rowOff>
+      <xdr:colOff>640069</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>10555</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B789239-5294-4E3C-A61E-52681F803A64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A1B9242-26CA-40F8-9D03-8C562B82B564}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4374,7 +4324,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="2571750"/>
-          <a:ext cx="13508335" cy="7344800"/>
+          <a:ext cx="13575019" cy="7382905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4778,7 +4728,7 @@
   <cols>
     <col min="1" max="1" width="10.125" customWidth="1"/>
     <col min="2" max="48" width="3.625" customWidth="1"/>
-    <col min="49" max="49" width="8.625" customWidth="1"/>
+    <col min="49" max="49" width="29.125" style="10" bestFit="1" customWidth="1"/>
     <col min="50" max="52" width="3.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4807,7 +4757,7 @@
       <c r="B7" t="s">
         <v>1</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="AW7" s="10" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4815,7 +4765,7 @@
       <c r="A49" s="9">
         <v>45870</v>
       </c>
-      <c r="AW49" s="9">
+      <c r="AW49" s="11">
         <v>45870</v>
       </c>
     </row>
@@ -4823,7 +4773,7 @@
       <c r="A50" t="s">
         <v>3</v>
       </c>
-      <c r="AW50" t="s">
+      <c r="AW50" s="10" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4831,7 +4781,7 @@
       <c r="A92" s="9">
         <v>45901</v>
       </c>
-      <c r="AW92" s="9">
+      <c r="AW92" s="11">
         <v>45901</v>
       </c>
     </row>
@@ -4839,7 +4789,7 @@
       <c r="A93" t="s">
         <v>3</v>
       </c>
-      <c r="AW93" t="s">
+      <c r="AW93" s="10" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4847,7 +4797,7 @@
       <c r="A135" s="9">
         <v>45536</v>
       </c>
-      <c r="AW135" s="9">
+      <c r="AW135" s="11">
         <v>45536</v>
       </c>
     </row>
@@ -4855,7 +4805,7 @@
       <c r="A136" t="s">
         <v>3</v>
       </c>
-      <c r="AW136" t="s">
+      <c r="AW136" s="10" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5089,7 +5039,8 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5154,7 +5105,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="148.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" ht="135" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -5366,18 +5317,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5539,6 +5490,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -5550,14 +5509,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
